--- a/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EF44" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F732" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="AC72" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F8F1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D00E" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D6C9" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F9A2" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E167" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="ED7A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F58A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="CAA5" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="90E5" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="F732" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9771" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="F8F1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B755" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D6C9" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F088" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E167" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EC83" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F58A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8F21" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="90E5" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="914D" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/mixs/spatial_transcriptomics_image_manifest_version_mixs_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="9771" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8925" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="B755" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C026" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F088" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B3B8" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC83" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B344" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8F21" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B9D1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="914D" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BC35" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
